--- a/omega60_master_config.xlsx
+++ b/omega60_master_config.xlsx
@@ -609,13 +609,13 @@
         <v>0.14</v>
       </c>
       <c r="U2" t="n">
-        <v>-6.818032138759492e-20</v>
+        <v>-7.964572372899748e-19</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.001113469147758561</v>
+        <v>-0.01300713377676727</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.005404892779437898</v>
+        <v>-0.0631379536404324</v>
       </c>
     </row>
     <row r="3">
@@ -682,13 +682,13 @@
         <v>0.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.045409641627878e-19</v>
+        <v>2.389371711869928e-18</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001113469147758561</v>
+        <v>0.01300713377676727</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.005404892779437898</v>
+        <v>-0.0631379536404324</v>
       </c>
     </row>
     <row r="4">
@@ -755,13 +755,13 @@
         <v>0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
     </row>
     <row r="5">
@@ -828,13 +828,13 @@
         <v>0.14</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
     </row>
     <row r="6">
@@ -901,13 +901,13 @@
         <v>0.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
       <c r="V6" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336356</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
     </row>
     <row r="7">
@@ -974,13 +974,13 @@
         <v>0.14</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="V7" t="n">
-        <v>0.002226938295502578</v>
+        <v>0.02601426755336367</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
     </row>
     <row r="8">
@@ -1047,13 +1047,13 @@
         <v>0.14</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
     </row>
     <row r="9">
@@ -1120,13 +1120,13 @@
         <v>0.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394963</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.001113469147755675</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
     </row>
     <row r="10">
@@ -1193,13 +1193,13 @@
         <v>0.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394985</v>
       </c>
       <c r="V10" t="n">
-        <v>0.001113469147755675</v>
+        <v>0.01300713377673463</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
     </row>
     <row r="11">
@@ -1266,13 +1266,13 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
       <c r="V11" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673468</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
     </row>
     <row r="12">
@@ -1339,13 +1339,13 @@
         <v>0.14</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
     </row>
     <row r="13">
@@ -1412,13 +1412,13 @@
         <v>0.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0.001113469147755675</v>
+        <v>0.01300713377673468</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
     </row>
     <row r="14">
@@ -1485,13 +1485,13 @@
         <v>0.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673474</v>
       </c>
       <c r="V14" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
     </row>
     <row r="15">
@@ -1558,13 +1558,13 @@
         <v>0.14</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="V15" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
     </row>
     <row r="16">
@@ -1631,13 +1631,13 @@
         <v>0.14</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
     </row>
     <row r="17">
@@ -1704,13 +1704,13 @@
         <v>0.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
     </row>
     <row r="18">
@@ -1777,13 +1777,13 @@
         <v>0.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="V18" t="n">
-        <v>0.001801630926430264</v>
+        <v>0.02104598454623885</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.002226938295502467</v>
+        <v>-0.02601426755336356</v>
       </c>
     </row>
     <row r="19">
@@ -1850,13 +1850,13 @@
         <v>0.14</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.004716731000723007</v>
+        <v>-0.05509910287046016</v>
       </c>
       <c r="V19" t="n">
-        <v>0.001801630926430264</v>
+        <v>0.02104598454623885</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.002226938295502467</v>
+        <v>-0.02601426755336356</v>
       </c>
     </row>
     <row r="20">
@@ -1923,13 +1923,13 @@
         <v>0.14</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
     </row>
     <row r="21">
@@ -1996,13 +1996,13 @@
         <v>0.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336356</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
     </row>
     <row r="22">
@@ -2069,13 +2069,13 @@
         <v>0.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0.002226938295502356</v>
+        <v>0.02601426755336345</v>
       </c>
       <c r="V22" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
     </row>
     <row r="23">
@@ -2142,13 +2142,13 @@
         <v>0.14</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.002226938295502356</v>
+        <v>-0.02601426755336333</v>
       </c>
       <c r="V23" t="n">
-        <v>0.004716731000723007</v>
+        <v>0.05509910287046016</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.001801630926430264</v>
+        <v>-0.02104598454623885</v>
       </c>
     </row>
     <row r="24">
@@ -2215,13 +2215,13 @@
         <v>0.14</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.005404892779437676</v>
+        <v>-0.06313795364043218</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.001113469147758506</v>
+        <v>-0.01300713377676721</v>
       </c>
     </row>
     <row r="25">
@@ -2288,13 +2288,13 @@
         <v>0.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0.005404892779437676</v>
+        <v>0.06313795364043218</v>
       </c>
       <c r="V25" t="n">
-        <v>-6.619084642073015e-19</v>
+        <v>-7.732169283046905e-18</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.001113469147758506</v>
+        <v>-0.01300713377676721</v>
       </c>
     </row>
     <row r="26">
@@ -2361,13 +2361,13 @@
         <v>0.14</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.001113469147755675</v>
+        <v>-0.01300713377673468</v>
       </c>
     </row>
     <row r="27">
@@ -2434,13 +2434,13 @@
         <v>0.14</v>
       </c>
       <c r="U27" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394985</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
     </row>
     <row r="28">
@@ -2507,13 +2507,13 @@
         <v>0.14</v>
       </c>
       <c r="U28" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="V28" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394963</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.001113469147755675</v>
+        <v>-0.01300713377673468</v>
       </c>
     </row>
     <row r="29">
@@ -2580,13 +2580,13 @@
         <v>0.14</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.004028569221949274</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="V29" t="n">
-        <v>0.003603261852986872</v>
+        <v>0.04209196909395008</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.001113469147755786</v>
+        <v>-0.01300713377673474</v>
       </c>
     </row>
     <row r="30">
@@ -2653,13 +2653,13 @@
         <v>0.14</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.001113469147758506</v>
+        <v>-0.01300713377676721</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.005404892779437676</v>
+        <v>-0.06313795364043218</v>
       </c>
       <c r="W30" t="n">
-        <v>-3.379042171560368e-19</v>
+        <v>-3.947271790269208e-18</v>
       </c>
     </row>
     <row r="31">
@@ -2726,13 +2726,13 @@
         <v>0.14</v>
       </c>
       <c r="U31" t="n">
-        <v>0.001113469147758561</v>
+        <v>0.01300713377676721</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.005404892779437676</v>
+        <v>-0.06313795364043218</v>
       </c>
       <c r="W31" t="n">
-        <v>-3.379042171560368e-19</v>
+        <v>-3.947271790269208e-18</v>
       </c>
     </row>
     <row r="32">
@@ -2799,13 +2799,13 @@
         <v>0.14</v>
       </c>
       <c r="U32" t="n">
-        <v>0.001113469147758617</v>
+        <v>0.01300713377676732</v>
       </c>
       <c r="V32" t="n">
-        <v>0.005404892779437898</v>
+        <v>0.0631379536404324</v>
       </c>
       <c r="W32" t="n">
-        <v>-3.379042171560491e-19</v>
+        <v>-3.947271790269232e-18</v>
       </c>
     </row>
     <row r="33">
@@ -2872,13 +2872,13 @@
         <v>0.14</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.001113469147758506</v>
+        <v>-0.01300713377676721</v>
       </c>
       <c r="V33" t="n">
-        <v>0.005404892779437676</v>
+        <v>0.06313795364043218</v>
       </c>
       <c r="W33" t="n">
-        <v>-3.379042171560368e-19</v>
+        <v>-3.947271790269208e-18</v>
       </c>
     </row>
     <row r="34">
@@ -2945,13 +2945,13 @@
         <v>0.14</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394963</v>
       </c>
       <c r="W34" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673468</v>
       </c>
     </row>
     <row r="35">
@@ -3018,13 +3018,13 @@
         <v>0.14</v>
       </c>
       <c r="U35" t="n">
-        <v>0.00402856922194883</v>
+        <v>0.04706025209979381</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394985</v>
       </c>
       <c r="W35" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673468</v>
       </c>
     </row>
     <row r="36">
@@ -3091,13 +3091,13 @@
         <v>0.14</v>
       </c>
       <c r="U36" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="V36" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394963</v>
       </c>
       <c r="W36" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673468</v>
       </c>
     </row>
     <row r="37">
@@ -3164,13 +3164,13 @@
         <v>0.14</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.004028569221949052</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="V37" t="n">
-        <v>0.00360326185298665</v>
+        <v>0.04209196909394985</v>
       </c>
       <c r="W37" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673474</v>
       </c>
     </row>
     <row r="38">
@@ -3237,13 +3237,13 @@
         <v>0.14</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.005404892779437676</v>
+        <v>-0.06313795364043218</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.001113469147758561</v>
+        <v>0.01300713377676721</v>
       </c>
     </row>
     <row r="39">
@@ -3310,13 +3310,13 @@
         <v>0.14</v>
       </c>
       <c r="U39" t="n">
-        <v>0.005404892779437676</v>
+        <v>0.06313795364043218</v>
       </c>
       <c r="V39" t="n">
-        <v>-6.619084642073015e-19</v>
+        <v>-7.732169283046905e-18</v>
       </c>
       <c r="W39" t="n">
-        <v>0.001113469147758561</v>
+        <v>0.01300713377676721</v>
       </c>
     </row>
     <row r="40">
@@ -3383,13 +3383,13 @@
         <v>0.14</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.002226938295502578</v>
+        <v>-0.02601426755336367</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="W40" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
     </row>
     <row r="41">
@@ -3456,13 +3456,13 @@
         <v>0.14</v>
       </c>
       <c r="U41" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336356</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="W41" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
     </row>
     <row r="42">
@@ -3529,13 +3529,13 @@
         <v>0.14</v>
       </c>
       <c r="U42" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336356</v>
       </c>
       <c r="V42" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="W42" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
     </row>
     <row r="43">
@@ -3602,13 +3602,13 @@
         <v>0.14</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.002226938295502467</v>
+        <v>-0.02601426755336356</v>
       </c>
       <c r="V43" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.0550991028704606</v>
       </c>
       <c r="W43" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
     </row>
     <row r="44">
@@ -3675,13 +3675,13 @@
         <v>0.14</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="W44" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336367</v>
       </c>
     </row>
     <row r="45">
@@ -3748,13 +3748,13 @@
         <v>0.14</v>
       </c>
       <c r="U45" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="V45" t="n">
-        <v>-0.001801630926430375</v>
+        <v>-0.02104598454623896</v>
       </c>
       <c r="W45" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336367</v>
       </c>
     </row>
     <row r="46">
@@ -3821,13 +3821,13 @@
         <v>0.14</v>
       </c>
       <c r="U46" t="n">
-        <v>0.004716731000723229</v>
+        <v>0.05509910287046038</v>
       </c>
       <c r="V46" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
       <c r="W46" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336367</v>
       </c>
     </row>
     <row r="47">
@@ -3894,13 +3894,13 @@
         <v>0.14</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.004716731000723229</v>
+        <v>-0.05509910287046038</v>
       </c>
       <c r="V47" t="n">
-        <v>0.001801630926430375</v>
+        <v>0.02104598454623896</v>
       </c>
       <c r="W47" t="n">
-        <v>0.002226938295502467</v>
+        <v>0.02601426755336367</v>
       </c>
     </row>
     <row r="48">
@@ -3967,13 +3967,13 @@
         <v>0.14</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673474</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.004028569221949274</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="W48" t="n">
-        <v>0.00360326185298665</v>
+        <v>0.04209196909394985</v>
       </c>
     </row>
     <row r="49">
@@ -4040,13 +4040,13 @@
         <v>0.14</v>
       </c>
       <c r="U49" t="n">
-        <v>0.001113469147755786</v>
+        <v>0.01300713377673474</v>
       </c>
       <c r="V49" t="n">
-        <v>-0.004028569221949274</v>
+        <v>-0.04706025209979403</v>
       </c>
       <c r="W49" t="n">
-        <v>0.003603261852986872</v>
+        <v>0.04209196909395008</v>
       </c>
     </row>
     <row r="50">
@@ -4113,13 +4113,13 @@
         <v>0.14</v>
       </c>
       <c r="U50" t="n">
-        <v>0.001113469147755786</v>
+        <v>0.01300713377673474</v>
       </c>
       <c r="V50" t="n">
-        <v>0.004028569221949052</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="W50" t="n">
-        <v>0.00360326185298665</v>
+        <v>0.04209196909394985</v>
       </c>
     </row>
     <row r="51">
@@ -4186,13 +4186,13 @@
         <v>0.14</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673474</v>
       </c>
       <c r="V51" t="n">
-        <v>0.004028569221949274</v>
+        <v>0.04706025209979403</v>
       </c>
       <c r="W51" t="n">
-        <v>0.00360326185298665</v>
+        <v>0.04209196909394985</v>
       </c>
     </row>
     <row r="52">
@@ -4259,13 +4259,13 @@
         <v>0.14</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394985</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="W52" t="n">
-        <v>0.00402856922194883</v>
+        <v>0.04706025209979381</v>
       </c>
     </row>
     <row r="53">
@@ -4332,13 +4332,13 @@
         <v>0.14</v>
       </c>
       <c r="U53" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394985</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.00111346914775573</v>
+        <v>-0.01300713377673468</v>
       </c>
       <c r="W53" t="n">
-        <v>0.00402856922194883</v>
+        <v>0.04706025209979381</v>
       </c>
     </row>
     <row r="54">
@@ -4405,13 +4405,13 @@
         <v>0.14</v>
       </c>
       <c r="U54" t="n">
-        <v>0.003603261852986428</v>
+        <v>0.04209196909394985</v>
       </c>
       <c r="V54" t="n">
-        <v>0.001113469147755675</v>
+        <v>0.01300713377673463</v>
       </c>
       <c r="W54" t="n">
-        <v>0.00402856922194883</v>
+        <v>0.04706025209979381</v>
       </c>
     </row>
     <row r="55">
@@ -4478,13 +4478,13 @@
         <v>0.14</v>
       </c>
       <c r="U55" t="n">
-        <v>-0.003603261852986428</v>
+        <v>-0.04209196909394985</v>
       </c>
       <c r="V55" t="n">
-        <v>0.00111346914775573</v>
+        <v>0.01300713377673468</v>
       </c>
       <c r="W55" t="n">
-        <v>0.00402856922194883</v>
+        <v>0.04706025209979381</v>
       </c>
     </row>
     <row r="56">
@@ -4551,13 +4551,13 @@
         <v>0.14</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.001801630926430264</v>
+        <v>-0.02104598454623885</v>
       </c>
       <c r="V56" t="n">
-        <v>-0.002226938295502356</v>
+        <v>-0.02601426755336345</v>
       </c>
       <c r="W56" t="n">
-        <v>0.004716731000722785</v>
+        <v>0.05509910287045994</v>
       </c>
     </row>
     <row r="57">
@@ -4624,13 +4624,13 @@
         <v>0.14</v>
       </c>
       <c r="U57" t="n">
-        <v>0.001801630926430264</v>
+        <v>0.02104598454623885</v>
       </c>
       <c r="V57" t="n">
-        <v>-0.002226938295502356</v>
+        <v>-0.02601426755336345</v>
       </c>
       <c r="W57" t="n">
-        <v>0.004716731000722785</v>
+        <v>0.05509910287045994</v>
       </c>
     </row>
     <row r="58">
@@ -4697,13 +4697,13 @@
         <v>0.14</v>
       </c>
       <c r="U58" t="n">
-        <v>0.001801630926430264</v>
+        <v>0.02104598454623885</v>
       </c>
       <c r="V58" t="n">
-        <v>0.002226938295502356</v>
+        <v>0.02601426755336345</v>
       </c>
       <c r="W58" t="n">
-        <v>0.004716731000722785</v>
+        <v>0.05509910287045994</v>
       </c>
     </row>
     <row r="59">
@@ -4770,13 +4770,13 @@
         <v>0.14</v>
       </c>
       <c r="U59" t="n">
-        <v>-0.001801630926430153</v>
+        <v>-0.02104598454623874</v>
       </c>
       <c r="V59" t="n">
-        <v>0.002226938295502356</v>
+        <v>0.02601426755336345</v>
       </c>
       <c r="W59" t="n">
-        <v>0.004716731000722785</v>
+        <v>0.05509910287045994</v>
       </c>
     </row>
     <row r="60">
@@ -4843,13 +4843,13 @@
         <v>0.14</v>
       </c>
       <c r="U60" t="n">
-        <v>-6.818032138758875e-20</v>
+        <v>-7.964572372899717e-19</v>
       </c>
       <c r="V60" t="n">
-        <v>-0.001113469147758561</v>
+        <v>-0.01300713377676727</v>
       </c>
       <c r="W60" t="n">
-        <v>0.005404892779437676</v>
+        <v>0.06313795364043218</v>
       </c>
     </row>
     <row r="61">
@@ -4916,13 +4916,13 @@
         <v>0.14</v>
       </c>
       <c r="U61" t="n">
-        <v>2.045409641627632e-19</v>
+        <v>2.389371711869915e-18</v>
       </c>
       <c r="V61" t="n">
-        <v>0.001113469147758561</v>
+        <v>0.01300713377676727</v>
       </c>
       <c r="W61" t="n">
-        <v>0.005404892779437676</v>
+        <v>0.06313795364043218</v>
       </c>
     </row>
   </sheetData>

--- a/omega60_master_config.xlsx
+++ b/omega60_master_config.xlsx
@@ -609,13 +609,13 @@
         <v>0.14</v>
       </c>
       <c r="U2" t="n">
-        <v>-7.964572372899748e-19</v>
+        <v>-2.059183443928331e-19</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.01300713377676727</v>
+        <v>-0.003362901769493054</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.0631379536404324</v>
+        <v>-0.01632386809143371</v>
       </c>
     </row>
     <row r="3">
@@ -682,13 +682,13 @@
         <v>0.14</v>
       </c>
       <c r="U3" t="n">
-        <v>2.389371711869928e-18</v>
+        <v>6.177550331784993e-19</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01300713377676727</v>
+        <v>0.003362901769493054</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0631379536404324</v>
+        <v>-0.01632386809143371</v>
       </c>
     </row>
     <row r="4">
@@ -755,13 +755,13 @@
         <v>0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
     </row>
     <row r="5">
@@ -828,13 +828,13 @@
         <v>0.14</v>
       </c>
       <c r="U5" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
     </row>
     <row r="6">
@@ -901,13 +901,13 @@
         <v>0.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
       <c r="V6" t="n">
-        <v>0.02601426755336356</v>
+        <v>0.00672580353894181</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
     </row>
     <row r="7">
@@ -974,13 +974,13 @@
         <v>0.14</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663282</v>
       </c>
       <c r="V7" t="n">
-        <v>0.02601426755336367</v>
+        <v>0.006725803538941921</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
     </row>
     <row r="8">
@@ -1047,13 +1047,13 @@
         <v>0.14</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
     </row>
     <row r="9">
@@ -1120,13 +1120,13 @@
         <v>0.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0.04209196909394963</v>
+        <v>0.01088257872770693</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
     </row>
     <row r="10">
@@ -1193,13 +1193,13 @@
         <v>0.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
       <c r="V10" t="n">
-        <v>0.01300713377673463</v>
+        <v>0.003362901769484505</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
     </row>
     <row r="11">
@@ -1266,13 +1266,13 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="V11" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484561</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
     </row>
     <row r="12">
@@ -1339,13 +1339,13 @@
         <v>0.14</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
     </row>
     <row r="13">
@@ -1412,13 +1412,13 @@
         <v>0.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484505</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
     </row>
     <row r="14">
@@ -1485,13 +1485,13 @@
         <v>0.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01300713377673474</v>
+        <v>0.003362901769484561</v>
       </c>
       <c r="V14" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
     </row>
     <row r="15">
@@ -1558,13 +1558,13 @@
         <v>0.14</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="V15" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
     </row>
     <row r="16">
@@ -1631,13 +1631,13 @@
         <v>0.14</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
     </row>
     <row r="17">
@@ -1704,13 +1704,13 @@
         <v>0.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
     </row>
     <row r="18">
@@ -1777,13 +1777,13 @@
         <v>0.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="V18" t="n">
-        <v>0.02104598454623885</v>
+        <v>0.005441289363663282</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.02601426755336356</v>
+        <v>-0.00672580353894181</v>
       </c>
     </row>
     <row r="19">
@@ -1850,13 +1850,13 @@
         <v>0.14</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.05509910287046016</v>
+        <v>-0.0142454804971337</v>
       </c>
       <c r="V19" t="n">
-        <v>0.02104598454623885</v>
+        <v>0.005441289363663282</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.02601426755336356</v>
+        <v>-0.00672580353894181</v>
       </c>
     </row>
     <row r="20">
@@ -1923,13 +1923,13 @@
         <v>0.14</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663282</v>
       </c>
     </row>
     <row r="21">
@@ -1996,13 +1996,13 @@
         <v>0.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0.02601426755336356</v>
+        <v>0.00672580353894181</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663282</v>
       </c>
     </row>
     <row r="22">
@@ -2069,13 +2069,13 @@
         <v>0.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0.02601426755336345</v>
+        <v>0.00672580353894181</v>
       </c>
       <c r="V22" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663282</v>
       </c>
     </row>
     <row r="23">
@@ -2142,13 +2142,13 @@
         <v>0.14</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.02601426755336333</v>
+        <v>-0.006725803538941699</v>
       </c>
       <c r="V23" t="n">
-        <v>0.05509910287046016</v>
+        <v>0.01424548049713348</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.02104598454623885</v>
+        <v>-0.005441289363663282</v>
       </c>
     </row>
     <row r="24">
@@ -2215,13 +2215,13 @@
         <v>0.14</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.06313795364043218</v>
+        <v>-0.01632386809143349</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.01300713377676721</v>
+        <v>-0.003362901769492943</v>
       </c>
     </row>
     <row r="25">
@@ -2288,13 +2288,13 @@
         <v>0.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0.06313795364043218</v>
+        <v>0.01632386809143349</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.732169283046905e-18</v>
+        <v>-1.999097280787755e-18</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.01300713377676721</v>
+        <v>-0.003362901769492943</v>
       </c>
     </row>
     <row r="26">
@@ -2361,13 +2361,13 @@
         <v>0.14</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484505</v>
       </c>
     </row>
     <row r="27">
@@ -2434,13 +2434,13 @@
         <v>0.14</v>
       </c>
       <c r="U27" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.04209196909394985</v>
+        <v>-0.01088257872770715</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
     </row>
     <row r="28">
@@ -2507,13 +2507,13 @@
         <v>0.14</v>
       </c>
       <c r="U28" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="V28" t="n">
-        <v>0.04209196909394963</v>
+        <v>0.01088257872770693</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484505</v>
       </c>
     </row>
     <row r="29">
@@ -2580,13 +2580,13 @@
         <v>0.14</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.01216709290265472</v>
       </c>
       <c r="V29" t="n">
-        <v>0.04209196909395008</v>
+        <v>0.01088257872770737</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.01300713377673474</v>
+        <v>-0.003362901769484616</v>
       </c>
     </row>
     <row r="30">
@@ -2653,13 +2653,13 @@
         <v>0.14</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.01300713377676721</v>
+        <v>-0.003362901769492943</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.06313795364043218</v>
+        <v>-0.01632386809143349</v>
       </c>
       <c r="W30" t="n">
-        <v>-3.947271790269208e-18</v>
+        <v>-1.020538999289455e-18</v>
       </c>
     </row>
     <row r="31">
@@ -2726,13 +2726,13 @@
         <v>0.14</v>
       </c>
       <c r="U31" t="n">
-        <v>0.01300713377676721</v>
+        <v>0.003362901769492999</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.06313795364043218</v>
+        <v>-0.01632386809143349</v>
       </c>
       <c r="W31" t="n">
-        <v>-3.947271790269208e-18</v>
+        <v>-1.020538999289455e-18</v>
       </c>
     </row>
     <row r="32">
@@ -2799,13 +2799,13 @@
         <v>0.14</v>
       </c>
       <c r="U32" t="n">
-        <v>0.01300713377676732</v>
+        <v>0.003362901769493054</v>
       </c>
       <c r="V32" t="n">
-        <v>0.0631379536404324</v>
+        <v>0.01632386809143371</v>
       </c>
       <c r="W32" t="n">
-        <v>-3.947271790269232e-18</v>
+        <v>-1.020538999289479e-18</v>
       </c>
     </row>
     <row r="33">
@@ -2872,13 +2872,13 @@
         <v>0.14</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.01300713377676721</v>
+        <v>-0.003362901769492999</v>
       </c>
       <c r="V33" t="n">
-        <v>0.06313795364043218</v>
+        <v>0.01632386809143349</v>
       </c>
       <c r="W33" t="n">
-        <v>-3.947271790269208e-18</v>
+        <v>-1.020538999289455e-18</v>
       </c>
     </row>
     <row r="34">
@@ -2945,13 +2945,13 @@
         <v>0.14</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.04209196909394963</v>
+        <v>-0.01088257872770693</v>
       </c>
       <c r="W34" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484561</v>
       </c>
     </row>
     <row r="35">
@@ -3018,13 +3018,13 @@
         <v>0.14</v>
       </c>
       <c r="U35" t="n">
-        <v>0.04706025209979381</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.04209196909394985</v>
+        <v>-0.01088257872770715</v>
       </c>
       <c r="W35" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484561</v>
       </c>
     </row>
     <row r="36">
@@ -3091,13 +3091,13 @@
         <v>0.14</v>
       </c>
       <c r="U36" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="V36" t="n">
-        <v>0.04209196909394963</v>
+        <v>0.01088257872770693</v>
       </c>
       <c r="W36" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484561</v>
       </c>
     </row>
     <row r="37">
@@ -3164,13 +3164,13 @@
         <v>0.14</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.0121670929026545</v>
       </c>
       <c r="V37" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
       <c r="W37" t="n">
-        <v>0.01300713377673474</v>
+        <v>0.003362901769484616</v>
       </c>
     </row>
     <row r="38">
@@ -3237,13 +3237,13 @@
         <v>0.14</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.06313795364043218</v>
+        <v>-0.01632386809143349</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.01300713377676721</v>
+        <v>0.003362901769492999</v>
       </c>
     </row>
     <row r="39">
@@ -3310,13 +3310,13 @@
         <v>0.14</v>
       </c>
       <c r="U39" t="n">
-        <v>0.06313795364043218</v>
+        <v>0.01632386809143349</v>
       </c>
       <c r="V39" t="n">
-        <v>-7.732169283046905e-18</v>
+        <v>-1.999097280787755e-18</v>
       </c>
       <c r="W39" t="n">
-        <v>0.01300713377676721</v>
+        <v>0.003362901769492999</v>
       </c>
     </row>
     <row r="40">
@@ -3383,13 +3383,13 @@
         <v>0.14</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.02601426755336367</v>
+        <v>-0.006725803538941921</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="W40" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
     </row>
     <row r="41">
@@ -3456,13 +3456,13 @@
         <v>0.14</v>
       </c>
       <c r="U41" t="n">
-        <v>0.02601426755336356</v>
+        <v>0.00672580353894181</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="W41" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
     </row>
     <row r="42">
@@ -3529,13 +3529,13 @@
         <v>0.14</v>
       </c>
       <c r="U42" t="n">
-        <v>0.02601426755336356</v>
+        <v>0.006725803538941921</v>
       </c>
       <c r="V42" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="W42" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
     </row>
     <row r="43">
@@ -3602,13 +3602,13 @@
         <v>0.14</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.02601426755336356</v>
+        <v>-0.006725803538941921</v>
       </c>
       <c r="V43" t="n">
-        <v>0.0550991028704606</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="W43" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
     </row>
     <row r="44">
@@ -3675,13 +3675,13 @@
         <v>0.14</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="W44" t="n">
-        <v>0.02601426755336367</v>
+        <v>0.006725803538941921</v>
       </c>
     </row>
     <row r="45">
@@ -3748,13 +3748,13 @@
         <v>0.14</v>
       </c>
       <c r="U45" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="V45" t="n">
-        <v>-0.02104598454623896</v>
+        <v>-0.005441289363663393</v>
       </c>
       <c r="W45" t="n">
-        <v>0.02601426755336367</v>
+        <v>0.006725803538941921</v>
       </c>
     </row>
     <row r="46">
@@ -3821,13 +3821,13 @@
         <v>0.14</v>
       </c>
       <c r="U46" t="n">
-        <v>0.05509910287046038</v>
+        <v>0.01424548049713392</v>
       </c>
       <c r="V46" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
       <c r="W46" t="n">
-        <v>0.02601426755336367</v>
+        <v>0.006725803538941921</v>
       </c>
     </row>
     <row r="47">
@@ -3894,13 +3894,13 @@
         <v>0.14</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.05509910287046038</v>
+        <v>-0.01424548049713392</v>
       </c>
       <c r="V47" t="n">
-        <v>0.02104598454623896</v>
+        <v>0.005441289363663393</v>
       </c>
       <c r="W47" t="n">
-        <v>0.02601426755336367</v>
+        <v>0.006725803538941921</v>
       </c>
     </row>
     <row r="48">
@@ -3967,13 +3967,13 @@
         <v>0.14</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.01300713377673474</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.01216709290265472</v>
       </c>
       <c r="W48" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
     </row>
     <row r="49">
@@ -4040,13 +4040,13 @@
         <v>0.14</v>
       </c>
       <c r="U49" t="n">
-        <v>0.01300713377673474</v>
+        <v>0.003362901769484616</v>
       </c>
       <c r="V49" t="n">
-        <v>-0.04706025209979403</v>
+        <v>-0.01216709290265472</v>
       </c>
       <c r="W49" t="n">
-        <v>0.04209196909395008</v>
+        <v>0.01088257872770737</v>
       </c>
     </row>
     <row r="50">
@@ -4113,13 +4113,13 @@
         <v>0.14</v>
       </c>
       <c r="U50" t="n">
-        <v>0.01300713377673474</v>
+        <v>0.003362901769484616</v>
       </c>
       <c r="V50" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.0121670929026545</v>
       </c>
       <c r="W50" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
     </row>
     <row r="51">
@@ -4186,13 +4186,13 @@
         <v>0.14</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.01300713377673474</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="V51" t="n">
-        <v>0.04706025209979403</v>
+        <v>0.01216709290265472</v>
       </c>
       <c r="W51" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
     </row>
     <row r="52">
@@ -4259,13 +4259,13 @@
         <v>0.14</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.04209196909394985</v>
+        <v>-0.01088257872770715</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="W52" t="n">
-        <v>0.04706025209979381</v>
+        <v>0.0121670929026545</v>
       </c>
     </row>
     <row r="53">
@@ -4332,13 +4332,13 @@
         <v>0.14</v>
       </c>
       <c r="U53" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.01300713377673468</v>
+        <v>-0.003362901769484561</v>
       </c>
       <c r="W53" t="n">
-        <v>0.04706025209979381</v>
+        <v>0.0121670929026545</v>
       </c>
     </row>
     <row r="54">
@@ -4405,13 +4405,13 @@
         <v>0.14</v>
       </c>
       <c r="U54" t="n">
-        <v>0.04209196909394985</v>
+        <v>0.01088257872770715</v>
       </c>
       <c r="V54" t="n">
-        <v>0.01300713377673463</v>
+        <v>0.003362901769484505</v>
       </c>
       <c r="W54" t="n">
-        <v>0.04706025209979381</v>
+        <v>0.0121670929026545</v>
       </c>
     </row>
     <row r="55">
@@ -4478,13 +4478,13 @@
         <v>0.14</v>
       </c>
       <c r="U55" t="n">
-        <v>-0.04209196909394985</v>
+        <v>-0.01088257872770715</v>
       </c>
       <c r="V55" t="n">
-        <v>0.01300713377673468</v>
+        <v>0.003362901769484561</v>
       </c>
       <c r="W55" t="n">
-        <v>0.04706025209979381</v>
+        <v>0.0121670929026545</v>
       </c>
     </row>
     <row r="56">
@@ -4551,13 +4551,13 @@
         <v>0.14</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.02104598454623885</v>
+        <v>-0.005441289363663282</v>
       </c>
       <c r="V56" t="n">
-        <v>-0.02601426755336345</v>
+        <v>-0.006725803538941699</v>
       </c>
       <c r="W56" t="n">
-        <v>0.05509910287045994</v>
+        <v>0.01424548049713348</v>
       </c>
     </row>
     <row r="57">
@@ -4624,13 +4624,13 @@
         <v>0.14</v>
       </c>
       <c r="U57" t="n">
-        <v>0.02104598454623885</v>
+        <v>0.005441289363663282</v>
       </c>
       <c r="V57" t="n">
-        <v>-0.02601426755336345</v>
+        <v>-0.006725803538941699</v>
       </c>
       <c r="W57" t="n">
-        <v>0.05509910287045994</v>
+        <v>0.01424548049713348</v>
       </c>
     </row>
     <row r="58">
@@ -4697,13 +4697,13 @@
         <v>0.14</v>
       </c>
       <c r="U58" t="n">
-        <v>0.02104598454623885</v>
+        <v>0.005441289363663282</v>
       </c>
       <c r="V58" t="n">
-        <v>0.02601426755336345</v>
+        <v>0.006725803538941699</v>
       </c>
       <c r="W58" t="n">
-        <v>0.05509910287045994</v>
+        <v>0.01424548049713348</v>
       </c>
     </row>
     <row r="59">
@@ -4770,13 +4770,13 @@
         <v>0.14</v>
       </c>
       <c r="U59" t="n">
-        <v>-0.02104598454623874</v>
+        <v>-0.005441289363663171</v>
       </c>
       <c r="V59" t="n">
-        <v>0.02601426755336345</v>
+        <v>0.006725803538941699</v>
       </c>
       <c r="W59" t="n">
-        <v>0.05509910287045994</v>
+        <v>0.01424548049713348</v>
       </c>
     </row>
     <row r="60">
@@ -4843,13 +4843,13 @@
         <v>0.14</v>
       </c>
       <c r="U60" t="n">
-        <v>-7.964572372899717e-19</v>
+        <v>-2.059183443928269e-19</v>
       </c>
       <c r="V60" t="n">
-        <v>-0.01300713377676727</v>
+        <v>-0.003362901769492999</v>
       </c>
       <c r="W60" t="n">
-        <v>0.06313795364043218</v>
+        <v>0.01632386809143349</v>
       </c>
     </row>
     <row r="61">
@@ -4916,13 +4916,13 @@
         <v>0.14</v>
       </c>
       <c r="U61" t="n">
-        <v>2.389371711869915e-18</v>
+        <v>6.177550331784869e-19</v>
       </c>
       <c r="V61" t="n">
-        <v>0.01300713377676727</v>
+        <v>0.003362901769492999</v>
       </c>
       <c r="W61" t="n">
-        <v>0.06313795364043218</v>
+        <v>0.01632386809143349</v>
       </c>
     </row>
   </sheetData>

--- a/omega60_master_config.xlsx
+++ b/omega60_master_config.xlsx
@@ -609,13 +609,13 @@
         <v>0.14</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.059183443928331e-19</v>
+        <v>-7.160131092033984e-20</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.003362901769493054</v>
+        <v>-0.001169338146642607</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.01632386809143371</v>
+        <v>-0.005676086596770658</v>
       </c>
     </row>
     <row r="3">
@@ -682,13 +682,13 @@
         <v>0.14</v>
       </c>
       <c r="U3" t="n">
-        <v>6.177550331784993e-19</v>
+        <v>2.148039327610195e-19</v>
       </c>
       <c r="V3" t="n">
-        <v>0.003362901769493054</v>
+        <v>0.001169338146642607</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.01632386809143371</v>
+        <v>-0.005676086596770658</v>
       </c>
     </row>
     <row r="4">
@@ -755,13 +755,13 @@
         <v>0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.005441289363663393</v>
+        <v>-0.001892028865538853</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
     </row>
     <row r="5">
@@ -828,13 +828,13 @@
         <v>0.14</v>
       </c>
       <c r="U5" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
     </row>
     <row r="6">
@@ -901,13 +901,13 @@
         <v>0.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
       <c r="V6" t="n">
-        <v>0.00672580353894181</v>
+        <v>0.002338676293269892</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
     </row>
     <row r="7">
@@ -974,13 +974,13 @@
         <v>0.14</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538742</v>
       </c>
       <c r="V7" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
     </row>
     <row r="8">
@@ -1047,13 +1047,13 @@
         <v>0.14</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
     </row>
     <row r="9">
@@ -1120,13 +1120,13 @@
         <v>0.14</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01088257872770693</v>
+        <v>0.0037840577312096</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
     </row>
     <row r="10">
@@ -1193,13 +1193,13 @@
         <v>0.14</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
       <c r="V10" t="n">
-        <v>0.003362901769484505</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
     </row>
     <row r="11">
@@ -1266,13 +1266,13 @@
         <v>0.14</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
       <c r="V11" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
     </row>
     <row r="12">
@@ -1339,13 +1339,13 @@
         <v>0.14</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
     </row>
     <row r="13">
@@ -1412,13 +1412,13 @@
         <v>0.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0.003362901769484505</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
     </row>
     <row r="14">
@@ -1485,13 +1485,13 @@
         <v>0.14</v>
       </c>
       <c r="U14" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="V14" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
     </row>
     <row r="15">
@@ -1558,13 +1558,13 @@
         <v>0.14</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
     </row>
     <row r="16">
@@ -1631,13 +1631,13 @@
         <v>0.14</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.005441289363663393</v>
+        <v>-0.001892028865538853</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
     </row>
     <row r="17">
@@ -1704,13 +1704,13 @@
         <v>0.14</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.005441289363663393</v>
+        <v>-0.001892028865538853</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
     </row>
     <row r="18">
@@ -1777,13 +1777,13 @@
         <v>0.14</v>
       </c>
       <c r="U18" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="V18" t="n">
-        <v>0.005441289363663282</v>
+        <v>0.001892028865538742</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.00672580353894181</v>
+        <v>-0.002338676293269781</v>
       </c>
     </row>
     <row r="19">
@@ -1850,13 +1850,13 @@
         <v>0.14</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0142454804971337</v>
+        <v>-0.00495339587782917</v>
       </c>
       <c r="V19" t="n">
-        <v>0.005441289363663282</v>
+        <v>0.001892028865538742</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.00672580353894181</v>
+        <v>-0.002338676293269781</v>
       </c>
     </row>
     <row r="20">
@@ -1923,13 +1923,13 @@
         <v>0.14</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538742</v>
       </c>
     </row>
     <row r="21">
@@ -1996,13 +1996,13 @@
         <v>0.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0.00672580353894181</v>
+        <v>0.002338676293269892</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538742</v>
       </c>
     </row>
     <row r="22">
@@ -2069,13 +2069,13 @@
         <v>0.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0.00672580353894181</v>
+        <v>0.002338676293269781</v>
       </c>
       <c r="V22" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538742</v>
       </c>
     </row>
     <row r="23">
@@ -2142,13 +2142,13 @@
         <v>0.14</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.006725803538941699</v>
+        <v>-0.00233867629326967</v>
       </c>
       <c r="V23" t="n">
-        <v>0.01424548049713348</v>
+        <v>0.00495339587782917</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538631</v>
       </c>
     </row>
     <row r="24">
@@ -2215,13 +2215,13 @@
         <v>0.14</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.01632386809143349</v>
+        <v>-0.005676086596770435</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.003362901769492943</v>
+        <v>-0.001169338146642551</v>
       </c>
     </row>
     <row r="25">
@@ -2288,13 +2288,13 @@
         <v>0.14</v>
       </c>
       <c r="U25" t="n">
-        <v>0.01632386809143349</v>
+        <v>0.005676086596770435</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.999097280787755e-18</v>
+        <v>-6.951201282417968e-19</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.003362901769492943</v>
+        <v>-0.001169338146642551</v>
       </c>
     </row>
     <row r="26">
@@ -2361,13 +2361,13 @@
         <v>0.14</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.003362901769484505</v>
+        <v>-0.001169338146639609</v>
       </c>
     </row>
     <row r="27">
@@ -2434,13 +2434,13 @@
         <v>0.14</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.003784057731209822</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639665</v>
       </c>
     </row>
     <row r="28">
@@ -2507,13 +2507,13 @@
         <v>0.14</v>
       </c>
       <c r="U28" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="V28" t="n">
-        <v>0.01088257872770693</v>
+        <v>0.0037840577312096</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.003362901769484505</v>
+        <v>-0.001169338146639609</v>
       </c>
     </row>
     <row r="29">
@@ -2580,13 +2580,13 @@
         <v>0.14</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.01216709290265472</v>
+        <v>-0.004230705158825954</v>
       </c>
       <c r="V29" t="n">
-        <v>0.01088257872770737</v>
+        <v>0.003784057731210044</v>
       </c>
       <c r="W29" t="n">
-        <v>-0.003362901769484616</v>
+        <v>-0.001169338146639665</v>
       </c>
     </row>
     <row r="30">
@@ -2653,13 +2653,13 @@
         <v>0.14</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.003362901769492943</v>
+        <v>-0.001169338146642551</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.01632386809143349</v>
+        <v>-0.005676086596770435</v>
       </c>
       <c r="W30" t="n">
-        <v>-1.020538999289455e-18</v>
+        <v>-3.548587689451071e-19</v>
       </c>
     </row>
     <row r="31">
@@ -2726,13 +2726,13 @@
         <v>0.14</v>
       </c>
       <c r="U31" t="n">
-        <v>0.003362901769492999</v>
+        <v>0.001169338146642607</v>
       </c>
       <c r="V31" t="n">
-        <v>-0.01632386809143349</v>
+        <v>-0.005676086596770435</v>
       </c>
       <c r="W31" t="n">
-        <v>-1.020538999289455e-18</v>
+        <v>-3.548587689451071e-19</v>
       </c>
     </row>
     <row r="32">
@@ -2799,13 +2799,13 @@
         <v>0.14</v>
       </c>
       <c r="U32" t="n">
-        <v>0.003362901769493054</v>
+        <v>0.001169338146642662</v>
       </c>
       <c r="V32" t="n">
-        <v>0.01632386809143371</v>
+        <v>0.005676086596770658</v>
       </c>
       <c r="W32" t="n">
-        <v>-1.020538999289479e-18</v>
+        <v>-3.548587689451195e-19</v>
       </c>
     </row>
     <row r="33">
@@ -2872,13 +2872,13 @@
         <v>0.14</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.003362901769492999</v>
+        <v>-0.001169338146642551</v>
       </c>
       <c r="V33" t="n">
-        <v>0.01632386809143349</v>
+        <v>0.005676086596770435</v>
       </c>
       <c r="W33" t="n">
-        <v>-1.020538999289455e-18</v>
+        <v>-3.548587689451071e-19</v>
       </c>
     </row>
     <row r="34">
@@ -2945,13 +2945,13 @@
         <v>0.14</v>
       </c>
       <c r="U34" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="V34" t="n">
-        <v>-0.01088257872770693</v>
+        <v>-0.0037840577312096</v>
       </c>
       <c r="W34" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
     </row>
     <row r="35">
@@ -3018,13 +3018,13 @@
         <v>0.14</v>
       </c>
       <c r="U35" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.00423070515882551</v>
       </c>
       <c r="V35" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.003784057731209822</v>
       </c>
       <c r="W35" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
     </row>
     <row r="36">
@@ -3091,13 +3091,13 @@
         <v>0.14</v>
       </c>
       <c r="U36" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="V36" t="n">
-        <v>0.01088257872770693</v>
+        <v>0.0037840577312096</v>
       </c>
       <c r="W36" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
     </row>
     <row r="37">
@@ -3164,13 +3164,13 @@
         <v>0.14</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.0121670929026545</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="V37" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
       <c r="W37" t="n">
-        <v>0.003362901769484616</v>
+        <v>0.001169338146639665</v>
       </c>
     </row>
     <row r="38">
@@ -3237,13 +3237,13 @@
         <v>0.14</v>
       </c>
       <c r="U38" t="n">
-        <v>-0.01632386809143349</v>
+        <v>-0.005676086596770435</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>0.003362901769492999</v>
+        <v>0.001169338146642607</v>
       </c>
     </row>
     <row r="39">
@@ -3310,13 +3310,13 @@
         <v>0.14</v>
       </c>
       <c r="U39" t="n">
-        <v>0.01632386809143349</v>
+        <v>0.005676086596770435</v>
       </c>
       <c r="V39" t="n">
-        <v>-1.999097280787755e-18</v>
+        <v>-6.951201282417968e-19</v>
       </c>
       <c r="W39" t="n">
-        <v>0.003362901769492999</v>
+        <v>0.001169338146642607</v>
       </c>
     </row>
     <row r="40">
@@ -3383,13 +3383,13 @@
         <v>0.14</v>
       </c>
       <c r="U40" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="W40" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
     </row>
     <row r="41">
@@ -3456,13 +3456,13 @@
         <v>0.14</v>
       </c>
       <c r="U41" t="n">
-        <v>0.00672580353894181</v>
+        <v>0.002338676293269892</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="W41" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
     </row>
     <row r="42">
@@ -3529,13 +3529,13 @@
         <v>0.14</v>
       </c>
       <c r="U42" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
       <c r="V42" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="W42" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
     </row>
     <row r="43">
@@ -3602,13 +3602,13 @@
         <v>0.14</v>
       </c>
       <c r="U43" t="n">
-        <v>-0.006725803538941921</v>
+        <v>-0.002338676293269892</v>
       </c>
       <c r="V43" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="W43" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
     </row>
     <row r="44">
@@ -3675,13 +3675,13 @@
         <v>0.14</v>
       </c>
       <c r="U44" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="V44" t="n">
-        <v>-0.005441289363663393</v>
+        <v>-0.001892028865538853</v>
       </c>
       <c r="W44" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
     </row>
     <row r="45">
@@ -3748,13 +3748,13 @@
         <v>0.14</v>
       </c>
       <c r="U45" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="V45" t="n">
-        <v>-0.005441289363663393</v>
+        <v>-0.001892028865538853</v>
       </c>
       <c r="W45" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
     </row>
     <row r="46">
@@ -3821,13 +3821,13 @@
         <v>0.14</v>
       </c>
       <c r="U46" t="n">
-        <v>0.01424548049713392</v>
+        <v>0.004953395877829392</v>
       </c>
       <c r="V46" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538742</v>
       </c>
       <c r="W46" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
     </row>
     <row r="47">
@@ -3894,13 +3894,13 @@
         <v>0.14</v>
       </c>
       <c r="U47" t="n">
-        <v>-0.01424548049713392</v>
+        <v>-0.004953395877829392</v>
       </c>
       <c r="V47" t="n">
-        <v>0.005441289363663393</v>
+        <v>0.001892028865538853</v>
       </c>
       <c r="W47" t="n">
-        <v>0.006725803538941921</v>
+        <v>0.002338676293269892</v>
       </c>
     </row>
     <row r="48">
@@ -3967,13 +3967,13 @@
         <v>0.14</v>
       </c>
       <c r="U48" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639665</v>
       </c>
       <c r="V48" t="n">
-        <v>-0.01216709290265472</v>
+        <v>-0.004230705158825732</v>
       </c>
       <c r="W48" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
     </row>
     <row r="49">
@@ -4040,13 +4040,13 @@
         <v>0.14</v>
       </c>
       <c r="U49" t="n">
-        <v>0.003362901769484616</v>
+        <v>0.001169338146639665</v>
       </c>
       <c r="V49" t="n">
-        <v>-0.01216709290265472</v>
+        <v>-0.004230705158825954</v>
       </c>
       <c r="W49" t="n">
-        <v>0.01088257872770737</v>
+        <v>0.003784057731210044</v>
       </c>
     </row>
     <row r="50">
@@ -4113,13 +4113,13 @@
         <v>0.14</v>
       </c>
       <c r="U50" t="n">
-        <v>0.003362901769484616</v>
+        <v>0.001169338146639665</v>
       </c>
       <c r="V50" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="W50" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
     </row>
     <row r="51">
@@ -4186,13 +4186,13 @@
         <v>0.14</v>
       </c>
       <c r="U51" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639665</v>
       </c>
       <c r="V51" t="n">
-        <v>0.01216709290265472</v>
+        <v>0.004230705158825732</v>
       </c>
       <c r="W51" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
     </row>
     <row r="52">
@@ -4259,13 +4259,13 @@
         <v>0.14</v>
       </c>
       <c r="U52" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.003784057731209822</v>
       </c>
       <c r="V52" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="W52" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.00423070515882551</v>
       </c>
     </row>
     <row r="53">
@@ -4332,13 +4332,13 @@
         <v>0.14</v>
       </c>
       <c r="U53" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.003784057731209822</v>
       </c>
       <c r="V53" t="n">
-        <v>-0.003362901769484561</v>
+        <v>-0.001169338146639609</v>
       </c>
       <c r="W53" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.00423070515882551</v>
       </c>
     </row>
     <row r="54">
@@ -4405,13 +4405,13 @@
         <v>0.14</v>
       </c>
       <c r="U54" t="n">
-        <v>0.01088257872770715</v>
+        <v>0.0037840577312096</v>
       </c>
       <c r="V54" t="n">
-        <v>0.003362901769484505</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="W54" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.00423070515882551</v>
       </c>
     </row>
     <row r="55">
@@ -4478,13 +4478,13 @@
         <v>0.14</v>
       </c>
       <c r="U55" t="n">
-        <v>-0.01088257872770715</v>
+        <v>-0.003784057731209822</v>
       </c>
       <c r="V55" t="n">
-        <v>0.003362901769484561</v>
+        <v>0.001169338146639609</v>
       </c>
       <c r="W55" t="n">
-        <v>0.0121670929026545</v>
+        <v>0.00423070515882551</v>
       </c>
     </row>
     <row r="56">
@@ -4551,13 +4551,13 @@
         <v>0.14</v>
       </c>
       <c r="U56" t="n">
-        <v>-0.005441289363663282</v>
+        <v>-0.001892028865538742</v>
       </c>
       <c r="V56" t="n">
-        <v>-0.006725803538941699</v>
+        <v>-0.00233867629326967</v>
       </c>
       <c r="W56" t="n">
-        <v>0.01424548049713348</v>
+        <v>0.004953395877828948</v>
       </c>
     </row>
     <row r="57">
@@ -4624,13 +4624,13 @@
         <v>0.14</v>
       </c>
       <c r="U57" t="n">
-        <v>0.005441289363663282</v>
+        <v>0.001892028865538742</v>
       </c>
       <c r="V57" t="n">
-        <v>-0.006725803538941699</v>
+        <v>-0.00233867629326967</v>
       </c>
       <c r="W57" t="n">
-        <v>0.01424548049713348</v>
+        <v>0.004953395877828948</v>
       </c>
     </row>
     <row r="58">
@@ -4697,13 +4697,13 @@
         <v>0.14</v>
       </c>
       <c r="U58" t="n">
-        <v>0.005441289363663282</v>
+        <v>0.001892028865538631</v>
       </c>
       <c r="V58" t="n">
-        <v>0.006725803538941699</v>
+        <v>0.00233867629326967</v>
       </c>
       <c r="W58" t="n">
-        <v>0.01424548049713348</v>
+        <v>0.004953395877828948</v>
       </c>
     </row>
     <row r="59">
@@ -4770,13 +4770,13 @@
         <v>0.14</v>
       </c>
       <c r="U59" t="n">
-        <v>-0.005441289363663171</v>
+        <v>-0.001892028865538631</v>
       </c>
       <c r="V59" t="n">
-        <v>0.006725803538941699</v>
+        <v>0.002338676293269781</v>
       </c>
       <c r="W59" t="n">
-        <v>0.01424548049713348</v>
+        <v>0.004953395877828948</v>
       </c>
     </row>
     <row r="60">
@@ -4843,13 +4843,13 @@
         <v>0.14</v>
       </c>
       <c r="U60" t="n">
-        <v>-2.059183443928269e-19</v>
+        <v>-7.160131092033676e-20</v>
       </c>
       <c r="V60" t="n">
-        <v>-0.003362901769492999</v>
+        <v>-0.001169338146642607</v>
       </c>
       <c r="W60" t="n">
-        <v>0.01632386809143349</v>
+        <v>0.005676086596770435</v>
       </c>
     </row>
     <row r="61">
@@ -4916,13 +4916,13 @@
         <v>0.14</v>
       </c>
       <c r="U61" t="n">
-        <v>6.177550331784869e-19</v>
+        <v>2.148039327610072e-19</v>
       </c>
       <c r="V61" t="n">
-        <v>0.003362901769492999</v>
+        <v>0.001169338146642607</v>
       </c>
       <c r="W61" t="n">
-        <v>0.01632386809143349</v>
+        <v>0.005676086596770435</v>
       </c>
     </row>
   </sheetData>
